--- a/docs/case_files/CASE_BROCCOLIF3B.xlsx
+++ b/docs/case_files/CASE_BROCCOLIF3B.xlsx
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX509"/>
+  <dimension ref="A1:AX516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="9" min="1" max="1"/>
@@ -66937,6 +66937,482 @@
         <is>
           <t>false</t>
         </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>0.0067458550159578</v>
+      </c>
+      <c r="C510">
+        <f>IFERROR(B510/B509-1,"")</f>
+        <v/>
+      </c>
+      <c r="D510" t="n">
+        <v>2060023.624491</v>
+      </c>
+      <c r="E510" t="n">
+        <v>46.305842</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0.0001769</v>
+      </c>
+      <c r="G510" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H510" t="n">
+        <v>0.0004607</v>
+      </c>
+      <c r="I510" t="n">
+        <v>6</v>
+      </c>
+      <c r="L510" t="n">
+        <v>2647764.8903136</v>
+      </c>
+      <c r="O510" t="n">
+        <v>1.6137</v>
+      </c>
+      <c r="P510" t="n">
+        <v>4.596</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>4.9595</v>
+      </c>
+      <c r="R510">
+        <f>IFERROR(O510/P510,"")</f>
+        <v/>
+      </c>
+      <c r="S510">
+        <f>IFERROR(AVERAGE(R508:R510),"")</f>
+        <v/>
+      </c>
+      <c r="T510">
+        <f>IFERROR(Q510/Q505,"")</f>
+        <v/>
+      </c>
+      <c r="U510">
+        <f>IFERROR(O510/O507-1,"")</f>
+        <v/>
+      </c>
+      <c r="V510">
+        <f>IFERROR(P510/P507-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ510">
+        <f>IF(OR(AB510="",D510="",D510=0),"",AB510/D510)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>0.0067728826243834</v>
+      </c>
+      <c r="C511">
+        <f>IFERROR(B511/B510-1,"")</f>
+        <v/>
+      </c>
+      <c r="D511" t="n">
+        <v>1488810.093969</v>
+      </c>
+      <c r="E511" t="n">
+        <v>49.758842</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0.0003901183333333</v>
+      </c>
+      <c r="G511" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H511" t="n">
+        <v>0.00116646</v>
+      </c>
+      <c r="I511" t="n">
+        <v>6</v>
+      </c>
+      <c r="L511" t="n">
+        <v>2461730.02095517</v>
+      </c>
+      <c r="O511" t="n">
+        <v>1.5813</v>
+      </c>
+      <c r="P511" t="n">
+        <v>5.0241</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>5.5359</v>
+      </c>
+      <c r="R511">
+        <f>IFERROR(O511/P511,"")</f>
+        <v/>
+      </c>
+      <c r="S511">
+        <f>IFERROR(AVERAGE(R509:R511),"")</f>
+        <v/>
+      </c>
+      <c r="T511">
+        <f>IFERROR(Q511/Q506,"")</f>
+        <v/>
+      </c>
+      <c r="U511">
+        <f>IFERROR(O511/O508-1,"")</f>
+        <v/>
+      </c>
+      <c r="V511">
+        <f>IFERROR(P511/P508-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ511">
+        <f>IF(OR(AB511="",D511="",D511=0),"",AB511/D511)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>0.0067917971038751</v>
+      </c>
+      <c r="C512">
+        <f>IFERROR(B512/B511-1,"")</f>
+        <v/>
+      </c>
+      <c r="D512" t="n">
+        <v>688949.323389</v>
+      </c>
+      <c r="E512" t="n">
+        <v>51.753751</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.0008642</v>
+      </c>
+      <c r="G512" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H512" t="n">
+        <v>0.00143918</v>
+      </c>
+      <c r="I512" t="n">
+        <v>6</v>
+      </c>
+      <c r="L512" t="n">
+        <v>2553626.25228</v>
+      </c>
+      <c r="O512" t="n">
+        <v>1.598</v>
+      </c>
+      <c r="P512" t="n">
+        <v>5.1881</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>6.2516</v>
+      </c>
+      <c r="R512">
+        <f>IFERROR(O512/P512,"")</f>
+        <v/>
+      </c>
+      <c r="S512">
+        <f>IFERROR(AVERAGE(R510:R512),"")</f>
+        <v/>
+      </c>
+      <c r="T512">
+        <f>IFERROR(Q512/Q507,"")</f>
+        <v/>
+      </c>
+      <c r="U512">
+        <f>IFERROR(O512/O509-1,"")</f>
+        <v/>
+      </c>
+      <c r="V512">
+        <f>IFERROR(P512/P509-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ512">
+        <f>IF(OR(AB512="",D512="",D512=0),"",AB512/D512)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>0.0068492703771687</v>
+      </c>
+      <c r="C513">
+        <f>IFERROR(B513/B512-1,"")</f>
+        <v/>
+      </c>
+      <c r="D513" t="n">
+        <v>684732.463644</v>
+      </c>
+      <c r="E513" t="n">
+        <v>48.937908</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0.0004198216666666</v>
+      </c>
+      <c r="G513" t="n">
+        <v>0.00010627</v>
+      </c>
+      <c r="H513" t="n">
+        <v>0.001286</v>
+      </c>
+      <c r="I513" t="n">
+        <v>6</v>
+      </c>
+      <c r="L513" t="n">
+        <v>2646942.811596</v>
+      </c>
+      <c r="O513" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="P513" t="n">
+        <v>5.4977</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>6.8003</v>
+      </c>
+      <c r="R513">
+        <f>IFERROR(O513/P513,"")</f>
+        <v/>
+      </c>
+      <c r="S513">
+        <f>IFERROR(AVERAGE(R511:R513),"")</f>
+        <v/>
+      </c>
+      <c r="T513">
+        <f>IFERROR(Q513/Q508,"")</f>
+        <v/>
+      </c>
+      <c r="U513">
+        <f>IFERROR(O513/O510-1,"")</f>
+        <v/>
+      </c>
+      <c r="V513">
+        <f>IFERROR(P513/P510-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ513">
+        <f>IF(OR(AB513="",D513="",D513=0),"",AB513/D513)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>0.0070685964220241</v>
+      </c>
+      <c r="C514">
+        <f>IFERROR(B514/B513-1,"")</f>
+        <v/>
+      </c>
+      <c r="D514" t="n">
+        <v>1042557.450926</v>
+      </c>
+      <c r="E514" t="n">
+        <v>47.739744</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0.000779325</v>
+      </c>
+      <c r="G514" t="n">
+        <v>0.00027538</v>
+      </c>
+      <c r="H514" t="n">
+        <v>0.00109551</v>
+      </c>
+      <c r="I514" t="n">
+        <v>6</v>
+      </c>
+      <c r="L514" t="n">
+        <v>2607025.742355</v>
+      </c>
+      <c r="O514" t="n">
+        <v>1.5201</v>
+      </c>
+      <c r="P514" t="n">
+        <v>5.6489</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>7.0128</v>
+      </c>
+      <c r="R514">
+        <f>IFERROR(O514/P514,"")</f>
+        <v/>
+      </c>
+      <c r="S514">
+        <f>IFERROR(AVERAGE(R512:R514),"")</f>
+        <v/>
+      </c>
+      <c r="T514">
+        <f>IFERROR(Q514/Q509,"")</f>
+        <v/>
+      </c>
+      <c r="U514">
+        <f>IFERROR(O514/O511-1,"")</f>
+        <v/>
+      </c>
+      <c r="V514">
+        <f>IFERROR(P514/P511-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ514">
+        <f>IF(OR(AB514="",D514="",D514=0),"",AB514/D514)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.0071588272348559</v>
+      </c>
+      <c r="C515">
+        <f>IFERROR(B515/B514-1,"")</f>
+        <v/>
+      </c>
+      <c r="D515" t="n">
+        <v>826236.911529</v>
+      </c>
+      <c r="E515" t="n">
+        <v>47.451393</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0.0005469116666666</v>
+      </c>
+      <c r="G515" t="n">
+        <v>-0.00014785</v>
+      </c>
+      <c r="H515" t="n">
+        <v>0.00129759</v>
+      </c>
+      <c r="I515" t="n">
+        <v>6</v>
+      </c>
+      <c r="L515" t="n">
+        <v>2659809.788748</v>
+      </c>
+      <c r="O515" t="n">
+        <v>1.5552</v>
+      </c>
+      <c r="P515" t="n">
+        <v>5.8871</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>7.285</v>
+      </c>
+      <c r="R515">
+        <f>IFERROR(O515/P515,"")</f>
+        <v/>
+      </c>
+      <c r="S515">
+        <f>IFERROR(AVERAGE(R513:R515),"")</f>
+        <v/>
+      </c>
+      <c r="T515">
+        <f>IFERROR(Q515/Q510,"")</f>
+        <v/>
+      </c>
+      <c r="U515">
+        <f>IFERROR(O515/O512-1,"")</f>
+        <v/>
+      </c>
+      <c r="V515">
+        <f>IFERROR(P515/P512-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ515">
+        <f>IF(OR(AB515="",D515="",D515=0),"",AB515/D515)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.007092592477395012</v>
+      </c>
+      <c r="C516">
+        <f>IFERROR(B516/B515-1,"")</f>
+        <v/>
+      </c>
+      <c r="D516" t="n">
+        <v>767842.160788</v>
+      </c>
+      <c r="E516" t="n">
+        <v>48.474856</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0.0006689333333333333</v>
+      </c>
+      <c r="G516" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H516" t="n">
+        <v>0.00146049</v>
+      </c>
+      <c r="I516" t="n">
+        <v>6</v>
+      </c>
+      <c r="L516" t="n">
+        <v>2723637.753888</v>
+      </c>
+      <c r="O516" t="n">
+        <v>1.5745</v>
+      </c>
+      <c r="P516" t="n">
+        <v>5.6622</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>6.9428</v>
+      </c>
+      <c r="R516">
+        <f>IFERROR(O516/P516,"")</f>
+        <v/>
+      </c>
+      <c r="S516">
+        <f>IFERROR(AVERAGE(R514:R516),"")</f>
+        <v/>
+      </c>
+      <c r="T516">
+        <f>IFERROR(Q516/Q511,"")</f>
+        <v/>
+      </c>
+      <c r="U516">
+        <f>IFERROR(O516/O513-1,"")</f>
+        <v/>
+      </c>
+      <c r="V516">
+        <f>IFERROR(P516/P513-1,"")</f>
+        <v/>
+      </c>
+      <c r="AJ516">
+        <f>IF(OR(AB516="",D516="",D516=0),"",AB516/D516)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
